--- a/human_validation/judge/kor/judge_D017_S001_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S001_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 스미스입니다. 만나서 반갑습니다. 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 저희 욕실에 더 밝은 거울을 설치한 이후로 볼과 턱 주위 피부가 계속 신경 쓰여서 왔어요. 제가 보기엔 고르지 않거나, 좀 처진 것처럼 보여요. 남편은 정말 무슨 말인지 모르겠다고 하는데, 저는 계속 그게 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 평균적으로 하루에 거울로 피부를 생각하거나 확인하는 데 몇 시간 정도 쓰신다고 말씀하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 총합으로 한 시간 정도, 주로 아침에요. 여러 각도에서 얼굴을 확인하고 법원에 가기 전에 화장을 좀 더 해요. 그런 다음 하루 중에 가끔 저도 모르게 직장 동료들과 제 얼굴을 비교하고 있거나, 기분이 안 좋으면 편안한 사진을 피하기도 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 남편분이 말씀하신 걸 못 보겠다고 할 때, 그분이 맞을 수도 있다고 생각하는 부분이 조금이라도 있으신가요, 아니면 그 결함이 정말로 보시는 그대로 존재한다고 완전히 확신하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 그러니까, 남편이 저와 같은 방식으로 못 볼 수도 있다는 건 알아요. 가끔은 제가 거기에 너무 집중하는 게 아닌가 싶기도 한데, 그래도 거울을 보면 여전히 꽤 뚜렷하게 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 신체이형장애 (D017)
 인구통계: 성별 여성 / 나이 46 / 직업상태 paralegal or legal assistant / 최종학력 고등학교 졸업
@@ -575,131 +642,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S067
-배경 서술: 레이다의 걱정은 그녀와 남편이 실용적인 집 개조의 일환으로 더 밝은 조명과 더 큰 거울을 추가하며 욕실을 리모델링한 후 눈에 띄기 시작했다. 아침 준비를 하는 동안, 그녀는 피부와 얼굴 윤곽의 미세한 변화라고 느끼는 것에 집착하기 시작했고, 이후 법원으로 출근하기 전에 확인하고 비교하는 작지만 지속적인 습관이 생겼다. 그녀는 여전히 업무에서 믿음직스러웠고 가족 요리, 정원 가꾸기, 독서 모임에도 활발히 참여했지만, 준비 시간이 늘어나면서 요가 수업에 늦거나 가끔 지역 행사에서 편안한 사진 촬영을 피하게 되었다. 그녀는 미용 시술 옵션에 대해 물어보러 갔던 1차 진료 방문에서 이 문제를 언급했고, 이 걱정이 기능적인 지장을 초래하고 있다는 것이 분명해지자 담당 의사가 그녀를 정신과 평가로 의뢰했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 스미스입니다. 만나서 반갑습니다. 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 저희 욕실에 더 밝은 거울을 설치한 이후로 볼과 턱 주위 피부가 계속 신경 쓰여서 왔어요. 제가 보기엔 고르지 않거나, 좀 처진 것처럼 보여요. 남편은 정말 무슨 말인지 모르겠다고 하는데, 저는 계속 그게 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 평균적으로 하루에 거울로 피부를 생각하거나 확인하는 데 몇 시간 정도 쓰신다고 말씀하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 총합으로 한 시간 정도, 주로 아침에요. 여러 각도에서 얼굴을 확인하고 법원에 가기 전에 화장을 좀 더 해요. 그런 다음 하루 중에 가끔 저도 모르게 직장 동료들과 제 얼굴을 비교하고 있거나, 기분이 안 좋으면 편안한 사진을 피하기도 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 남편분이 말씀하신 걸 못 보겠다고 할 때, 그분이 맞을 수도 있다고 생각하는 부분이 조금이라도 있으신가요, 아니면 그 결함이 정말로 보시는 그대로 존재한다고 완전히 확신하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 그러니까, 남편이 저와 같은 방식으로 못 볼 수도 있다는 건 알아요. 가끔은 제가 거기에 너무 집중하는 게 아닌가 싶기도 한데, 그래도 거울을 보면 여전히 꽤 뚜렷하게 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 레이다의 걱정은 그녀와 남편이 실용적인 집 개조의 일환으로 더 밝은 조명과 더 큰 거울을 추가하며 욕실을 리모델링한 후 눈에 띄기 시작했다. 아침 준비를 하는 동안, 그녀는 피부와 얼굴 윤곽의 미세한 변화라고 느끼는 것에 집착하기 시작했고, 이후 법원으로 출근하기 전에 확인하고 비교하는 작지만 지속적인 습관이 생겼다. 그녀는 여전히 업무에서 믿음직스러웠고 가족 요리, 정원 가꾸기, 독서 모임에도 활발히 참여했지만, 준비 시간이 늘어나면서 요가 수업에 늦거나 가끔 지역 행사에서 편안한 사진 촬영을 피하게 되었다. 그녀는 미용 시술 옵션에 대해 물어보러 갔던 1차 진료 방문에서 이 문제를 언급했고, 이 걱정이 기능적인 지장을 초래하고 있다는 것이 분명해지자 담당 의사가 그녀를 정신과 평가로 의뢰했다.
+표집된 증상 목록:
+  - S067 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - S068 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.; 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S001_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S001_P003__claude-sonnet-5_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -662,11 +667,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S001_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S001_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
